--- a/Files/TestFiles/BigBoard.xlsx
+++ b/Files/TestFiles/BigBoard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/40f61192ff96ff75/Documents/Git/MaddenDraftTool/Files/TestFiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{AC1A784E-2B35-4F80-A53E-87F276815A9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93F5BA36-D9FC-49A0-9ECA-823726EA9D16}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="8_{AC1A784E-2B35-4F80-A53E-87F276815A9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7C45AC7-5A25-42A3-8C20-16EB5EF4D708}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4043,7 +4043,7 @@
         <v>721</v>
       </c>
       <c r="E4" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -4066,7 +4066,7 @@
         <v>722</v>
       </c>
       <c r="E5" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -4089,7 +4089,7 @@
         <v>723</v>
       </c>
       <c r="E6" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4158,7 +4158,7 @@
         <v>726</v>
       </c>
       <c r="E9" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="F9">
         <v>8</v>

--- a/Files/TestFiles/BigBoard.xlsx
+++ b/Files/TestFiles/BigBoard.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/40f61192ff96ff75/Documents/Git/MaddenDraftTool/Files/TestFiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="8_{AC1A784E-2B35-4F80-A53E-87F276815A9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33194E1B-A932-4556-822B-AF3C9417FB8F}"/>
+  <xr:revisionPtr revIDLastSave="60" documentId="8_{AC1A784E-2B35-4F80-A53E-87F276815A9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7FF4B8C-93EF-4B12-8952-FD9769B08CB0}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BigBoardTeam" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2284" uniqueCount="1354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2284" uniqueCount="1357">
   <si>
     <t>LastName</t>
   </si>
@@ -3566,9 +3566,6 @@
     <t>Can'tMiss</t>
   </si>
   <si>
-    <t>BlueChip</t>
-  </si>
-  <si>
     <t>Standard</t>
   </si>
   <si>
@@ -4098,6 +4095,18 @@
   </si>
   <si>
     <t>gen_2_T_N_02</t>
+  </si>
+  <si>
+    <t>BlueChipPrem</t>
+  </si>
+  <si>
+    <t>BlueChipNonPrem</t>
+  </si>
+  <si>
+    <t>TopPrem</t>
+  </si>
+  <si>
+    <t>TopNonPrem</t>
   </si>
 </sst>
 </file>
@@ -4486,7 +4495,7 @@
     <col min="3" max="3" width="25.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25.125" customWidth="1"/>
     <col min="5" max="5" width="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.25" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.75" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
@@ -4503,7 +4512,7 @@
         <v>718</v>
       </c>
       <c r="D1" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="E1" t="s">
         <v>716</v>
@@ -4532,7 +4541,7 @@
         <v>719</v>
       </c>
       <c r="D2" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="F2" t="s">
         <v>1175</v>
@@ -4558,10 +4567,10 @@
         <v>720</v>
       </c>
       <c r="D3" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="F3" t="s">
-        <v>1176</v>
+        <v>1353</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -4584,10 +4593,10 @@
         <v>721</v>
       </c>
       <c r="D4" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="F4" t="s">
-        <v>1177</v>
+        <v>1355</v>
       </c>
       <c r="G4">
         <v>3</v>
@@ -4610,10 +4619,10 @@
         <v>722</v>
       </c>
       <c r="D5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="F5" t="s">
-        <v>1177</v>
+        <v>1355</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -4636,10 +4645,10 @@
         <v>723</v>
       </c>
       <c r="D6" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="F6" t="s">
-        <v>1177</v>
+        <v>1354</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4662,10 +4671,10 @@
         <v>724</v>
       </c>
       <c r="D7" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="F7" t="s">
-        <v>1177</v>
+        <v>1355</v>
       </c>
       <c r="G7">
         <v>6</v>
@@ -4688,10 +4697,10 @@
         <v>725</v>
       </c>
       <c r="D8" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="F8" t="s">
-        <v>1177</v>
+        <v>1355</v>
       </c>
       <c r="G8">
         <v>7</v>
@@ -4714,10 +4723,10 @@
         <v>726</v>
       </c>
       <c r="D9" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="F9" t="s">
-        <v>1176</v>
+        <v>1356</v>
       </c>
       <c r="G9">
         <v>8</v>
@@ -4740,10 +4749,10 @@
         <v>727</v>
       </c>
       <c r="D10" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="F10" t="s">
-        <v>1177</v>
+        <v>1355</v>
       </c>
       <c r="G10">
         <v>9</v>
@@ -4766,10 +4775,10 @@
         <v>728</v>
       </c>
       <c r="D11" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="F11" t="s">
-        <v>1177</v>
+        <v>1355</v>
       </c>
       <c r="G11">
         <v>10</v>
@@ -4792,10 +4801,10 @@
         <v>729</v>
       </c>
       <c r="D12" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="F12" t="s">
-        <v>1177</v>
+        <v>1356</v>
       </c>
       <c r="G12">
         <v>11</v>
@@ -4818,10 +4827,10 @@
         <v>730</v>
       </c>
       <c r="D13" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="F13" t="s">
-        <v>1177</v>
+        <v>1355</v>
       </c>
       <c r="G13">
         <v>12</v>
@@ -4844,10 +4853,10 @@
         <v>731</v>
       </c>
       <c r="D14" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="F14" t="s">
-        <v>1177</v>
+        <v>1355</v>
       </c>
       <c r="G14">
         <v>13</v>
@@ -4870,10 +4879,10 @@
         <v>732</v>
       </c>
       <c r="D15" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="F15" t="s">
-        <v>1177</v>
+        <v>1355</v>
       </c>
       <c r="G15">
         <v>14</v>
@@ -4896,10 +4905,10 @@
         <v>733</v>
       </c>
       <c r="D16" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="F16" t="s">
-        <v>1177</v>
+        <v>1356</v>
       </c>
       <c r="G16">
         <v>15</v>
@@ -4922,10 +4931,10 @@
         <v>734</v>
       </c>
       <c r="D17" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="F17" t="s">
-        <v>1177</v>
+        <v>1355</v>
       </c>
       <c r="G17">
         <v>16</v>
@@ -4948,10 +4957,10 @@
         <v>735</v>
       </c>
       <c r="D18" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="F18" t="s">
-        <v>1177</v>
+        <v>1355</v>
       </c>
       <c r="G18">
         <v>17</v>
@@ -4974,10 +4983,10 @@
         <v>736</v>
       </c>
       <c r="D19" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="F19" t="s">
-        <v>1177</v>
+        <v>1355</v>
       </c>
       <c r="G19">
         <v>18</v>
@@ -5000,10 +5009,10 @@
         <v>737</v>
       </c>
       <c r="D20" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="F20" t="s">
-        <v>1177</v>
+        <v>1356</v>
       </c>
       <c r="G20">
         <v>19</v>
@@ -5026,10 +5035,10 @@
         <v>738</v>
       </c>
       <c r="D21" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="F21" t="s">
-        <v>1177</v>
+        <v>1355</v>
       </c>
       <c r="G21">
         <v>20</v>
@@ -5052,10 +5061,10 @@
         <v>739</v>
       </c>
       <c r="D22" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="F22" t="s">
-        <v>1177</v>
+        <v>1355</v>
       </c>
       <c r="G22">
         <v>21</v>
@@ -5078,10 +5087,10 @@
         <v>740</v>
       </c>
       <c r="D23" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="F23" t="s">
-        <v>1177</v>
+        <v>1355</v>
       </c>
       <c r="G23">
         <v>22</v>
@@ -5104,10 +5113,10 @@
         <v>741</v>
       </c>
       <c r="D24" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="F24" t="s">
-        <v>1177</v>
+        <v>1355</v>
       </c>
       <c r="G24">
         <v>23</v>
@@ -5130,10 +5139,10 @@
         <v>742</v>
       </c>
       <c r="D25" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="F25" t="s">
-        <v>1177</v>
+        <v>1356</v>
       </c>
       <c r="G25">
         <v>24</v>
@@ -5156,10 +5165,10 @@
         <v>743</v>
       </c>
       <c r="D26" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="s">
-        <v>1177</v>
+        <v>1355</v>
       </c>
       <c r="G26">
         <v>25</v>
@@ -5182,10 +5191,10 @@
         <v>744</v>
       </c>
       <c r="D27" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="F27" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G27">
         <v>26</v>
@@ -5208,10 +5217,10 @@
         <v>745</v>
       </c>
       <c r="D28" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="F28" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G28">
         <v>27</v>
@@ -5234,10 +5243,10 @@
         <v>746</v>
       </c>
       <c r="D29" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="F29" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G29">
         <v>28</v>
@@ -5260,10 +5269,10 @@
         <v>747</v>
       </c>
       <c r="D30" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="F30" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G30">
         <v>29</v>
@@ -5286,10 +5295,10 @@
         <v>748</v>
       </c>
       <c r="D31" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="F31" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G31">
         <v>30</v>
@@ -5312,10 +5321,10 @@
         <v>749</v>
       </c>
       <c r="D32" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="F32" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G32">
         <v>31</v>
@@ -5338,10 +5347,10 @@
         <v>750</v>
       </c>
       <c r="D33" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="F33" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G33">
         <v>32</v>
@@ -5364,10 +5373,10 @@
         <v>751</v>
       </c>
       <c r="D34" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="F34" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G34">
         <v>33</v>
@@ -5390,10 +5399,10 @@
         <v>752</v>
       </c>
       <c r="D35" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="F35" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G35">
         <v>34</v>
@@ -5416,10 +5425,10 @@
         <v>753</v>
       </c>
       <c r="D36" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="F36" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G36">
         <v>35</v>
@@ -5442,10 +5451,10 @@
         <v>754</v>
       </c>
       <c r="D37" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F37" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G37">
         <v>36</v>
@@ -5468,10 +5477,10 @@
         <v>755</v>
       </c>
       <c r="D38" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="F38" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G38">
         <v>37</v>
@@ -5494,10 +5503,10 @@
         <v>756</v>
       </c>
       <c r="D39" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="F39" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G39">
         <v>38</v>
@@ -5520,10 +5529,10 @@
         <v>757</v>
       </c>
       <c r="D40" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="F40" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G40">
         <v>39</v>
@@ -5546,10 +5555,10 @@
         <v>758</v>
       </c>
       <c r="D41" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="F41" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G41">
         <v>40</v>
@@ -5572,10 +5581,10 @@
         <v>759</v>
       </c>
       <c r="D42" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="F42" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G42">
         <v>41</v>
@@ -5598,10 +5607,10 @@
         <v>760</v>
       </c>
       <c r="D43" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="F43" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G43">
         <v>42</v>
@@ -5624,10 +5633,10 @@
         <v>761</v>
       </c>
       <c r="D44" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="F44" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G44">
         <v>43</v>
@@ -5650,10 +5659,10 @@
         <v>762</v>
       </c>
       <c r="D45" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="F45" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G45">
         <v>44</v>
@@ -5676,10 +5685,10 @@
         <v>763</v>
       </c>
       <c r="D46" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="F46" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G46">
         <v>45</v>
@@ -5702,10 +5711,10 @@
         <v>764</v>
       </c>
       <c r="D47" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="F47" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G47">
         <v>46</v>
@@ -5728,10 +5737,10 @@
         <v>765</v>
       </c>
       <c r="D48" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="F48" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G48">
         <v>47</v>
@@ -5754,10 +5763,10 @@
         <v>766</v>
       </c>
       <c r="D49" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="F49" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G49">
         <v>48</v>
@@ -5780,10 +5789,10 @@
         <v>767</v>
       </c>
       <c r="D50" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="F50" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G50">
         <v>49</v>
@@ -5806,10 +5815,10 @@
         <v>768</v>
       </c>
       <c r="D51" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="F51" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G51">
         <v>50</v>
@@ -5832,10 +5841,10 @@
         <v>769</v>
       </c>
       <c r="D52" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F52" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G52">
         <v>51</v>
@@ -5858,10 +5867,10 @@
         <v>770</v>
       </c>
       <c r="D53" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="F53" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G53">
         <v>52</v>
@@ -5884,10 +5893,10 @@
         <v>771</v>
       </c>
       <c r="D54" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="F54" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G54">
         <v>53</v>
@@ -5910,10 +5919,10 @@
         <v>772</v>
       </c>
       <c r="D55" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="F55" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G55">
         <v>54</v>
@@ -5936,10 +5945,10 @@
         <v>773</v>
       </c>
       <c r="D56" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="F56" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G56">
         <v>55</v>
@@ -5962,10 +5971,10 @@
         <v>774</v>
       </c>
       <c r="D57" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="F57" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G57">
         <v>56</v>
@@ -5988,10 +5997,10 @@
         <v>775</v>
       </c>
       <c r="D58" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="F58" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G58">
         <v>57</v>
@@ -6014,10 +6023,10 @@
         <v>776</v>
       </c>
       <c r="D59" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="F59" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G59">
         <v>58</v>
@@ -6040,10 +6049,10 @@
         <v>777</v>
       </c>
       <c r="D60" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="F60" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G60">
         <v>59</v>
@@ -6066,10 +6075,10 @@
         <v>778</v>
       </c>
       <c r="D61" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="F61" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G61">
         <v>60</v>
@@ -6092,10 +6101,10 @@
         <v>779</v>
       </c>
       <c r="D62" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="F62" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G62">
         <v>61</v>
@@ -6118,10 +6127,10 @@
         <v>780</v>
       </c>
       <c r="D63" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="F63" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G63">
         <v>62</v>
@@ -6144,10 +6153,10 @@
         <v>781</v>
       </c>
       <c r="D64" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="F64" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G64">
         <v>63</v>
@@ -6170,10 +6179,10 @@
         <v>782</v>
       </c>
       <c r="D65" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="F65" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G65">
         <v>64</v>
@@ -6196,10 +6205,10 @@
         <v>783</v>
       </c>
       <c r="D66" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="F66" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G66">
         <v>65</v>
@@ -6222,10 +6231,10 @@
         <v>784</v>
       </c>
       <c r="D67" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="F67" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G67">
         <v>66</v>
@@ -6248,10 +6257,10 @@
         <v>785</v>
       </c>
       <c r="D68" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="F68" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G68">
         <v>67</v>
@@ -6274,10 +6283,10 @@
         <v>786</v>
       </c>
       <c r="D69" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F69" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G69">
         <v>68</v>
@@ -6300,10 +6309,10 @@
         <v>787</v>
       </c>
       <c r="D70" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G70">
         <v>69</v>
@@ -6326,10 +6335,10 @@
         <v>788</v>
       </c>
       <c r="D71" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="F71" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G71">
         <v>70</v>
@@ -6352,10 +6361,10 @@
         <v>789</v>
       </c>
       <c r="D72" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="F72" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G72">
         <v>71</v>
@@ -6378,10 +6387,10 @@
         <v>790</v>
       </c>
       <c r="D73" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="F73" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G73">
         <v>72</v>
@@ -6404,10 +6413,10 @@
         <v>791</v>
       </c>
       <c r="D74" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="F74" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G74">
         <v>73</v>
@@ -6430,10 +6439,10 @@
         <v>792</v>
       </c>
       <c r="D75" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F75" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G75">
         <v>74</v>
@@ -6456,10 +6465,10 @@
         <v>793</v>
       </c>
       <c r="D76" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F76" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G76">
         <v>75</v>
@@ -6482,10 +6491,10 @@
         <v>794</v>
       </c>
       <c r="D77" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="F77" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G77">
         <v>76</v>
@@ -6508,10 +6517,10 @@
         <v>795</v>
       </c>
       <c r="D78" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="F78" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G78">
         <v>77</v>
@@ -6534,10 +6543,10 @@
         <v>796</v>
       </c>
       <c r="D79" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="F79" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G79">
         <v>78</v>
@@ -6560,10 +6569,10 @@
         <v>797</v>
       </c>
       <c r="D80" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="F80" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G80">
         <v>79</v>
@@ -6586,10 +6595,10 @@
         <v>798</v>
       </c>
       <c r="D81" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="F81" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G81">
         <v>80</v>
@@ -6612,10 +6621,10 @@
         <v>799</v>
       </c>
       <c r="D82" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="F82" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G82">
         <v>81</v>
@@ -6638,10 +6647,10 @@
         <v>800</v>
       </c>
       <c r="D83" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="F83" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G83">
         <v>82</v>
@@ -6664,10 +6673,10 @@
         <v>801</v>
       </c>
       <c r="D84" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="F84" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G84">
         <v>83</v>
@@ -6690,10 +6699,10 @@
         <v>802</v>
       </c>
       <c r="D85" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="F85" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G85">
         <v>84</v>
@@ -6716,10 +6725,10 @@
         <v>803</v>
       </c>
       <c r="D86" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="F86" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G86">
         <v>85</v>
@@ -6742,10 +6751,10 @@
         <v>804</v>
       </c>
       <c r="D87" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="F87" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G87">
         <v>86</v>
@@ -6768,10 +6777,10 @@
         <v>805</v>
       </c>
       <c r="D88" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="F88" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G88">
         <v>87</v>
@@ -6794,10 +6803,10 @@
         <v>806</v>
       </c>
       <c r="D89" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="F89" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G89">
         <v>88</v>
@@ -6820,10 +6829,10 @@
         <v>807</v>
       </c>
       <c r="D90" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="F90" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G90">
         <v>89</v>
@@ -6846,10 +6855,10 @@
         <v>808</v>
       </c>
       <c r="D91" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="F91" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G91">
         <v>90</v>
@@ -6872,10 +6881,10 @@
         <v>809</v>
       </c>
       <c r="D92" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="F92" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G92">
         <v>91</v>
@@ -6898,10 +6907,10 @@
         <v>810</v>
       </c>
       <c r="D93" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="F93" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G93">
         <v>92</v>
@@ -6924,10 +6933,10 @@
         <v>811</v>
       </c>
       <c r="D94" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="F94" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G94">
         <v>93</v>
@@ -6950,10 +6959,10 @@
         <v>812</v>
       </c>
       <c r="D95" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="F95" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G95">
         <v>94</v>
@@ -6976,10 +6985,10 @@
         <v>813</v>
       </c>
       <c r="D96" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="F96" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G96">
         <v>95</v>
@@ -7002,10 +7011,10 @@
         <v>814</v>
       </c>
       <c r="D97" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="F97" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G97">
         <v>96</v>
@@ -7028,10 +7037,10 @@
         <v>815</v>
       </c>
       <c r="D98" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="F98" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G98">
         <v>97</v>
@@ -7054,10 +7063,10 @@
         <v>816</v>
       </c>
       <c r="D99" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="F99" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G99">
         <v>98</v>
@@ -7080,10 +7089,10 @@
         <v>817</v>
       </c>
       <c r="D100" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F100" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G100">
         <v>99</v>
@@ -7106,10 +7115,10 @@
         <v>818</v>
       </c>
       <c r="D101" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F101" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G101">
         <v>100</v>
@@ -7132,10 +7141,10 @@
         <v>819</v>
       </c>
       <c r="D102" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="F102" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G102">
         <v>101</v>
@@ -7158,10 +7167,10 @@
         <v>820</v>
       </c>
       <c r="D103" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="F103" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G103">
         <v>102</v>
@@ -7184,10 +7193,10 @@
         <v>821</v>
       </c>
       <c r="D104" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="F104" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G104">
         <v>103</v>
@@ -7210,10 +7219,10 @@
         <v>822</v>
       </c>
       <c r="D105" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="F105" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G105">
         <v>104</v>
@@ -7236,10 +7245,10 @@
         <v>823</v>
       </c>
       <c r="D106" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="F106" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G106">
         <v>105</v>
@@ -7262,10 +7271,10 @@
         <v>824</v>
       </c>
       <c r="D107" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="F107" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G107">
         <v>106</v>
@@ -7288,10 +7297,10 @@
         <v>825</v>
       </c>
       <c r="D108" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="F108" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G108">
         <v>107</v>
@@ -7314,10 +7323,10 @@
         <v>826</v>
       </c>
       <c r="D109" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="F109" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G109">
         <v>108</v>
@@ -7340,10 +7349,10 @@
         <v>827</v>
       </c>
       <c r="D110" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="F110" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G110">
         <v>109</v>
@@ -7366,10 +7375,10 @@
         <v>828</v>
       </c>
       <c r="D111" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F111" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G111">
         <v>110</v>
@@ -7392,10 +7401,10 @@
         <v>829</v>
       </c>
       <c r="D112" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="F112" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G112">
         <v>111</v>
@@ -7418,10 +7427,10 @@
         <v>830</v>
       </c>
       <c r="D113" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="F113" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G113">
         <v>112</v>
@@ -7444,10 +7453,10 @@
         <v>831</v>
       </c>
       <c r="D114" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="F114" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G114">
         <v>113</v>
@@ -7470,10 +7479,10 @@
         <v>832</v>
       </c>
       <c r="D115" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="F115" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G115">
         <v>114</v>
@@ -7496,10 +7505,10 @@
         <v>833</v>
       </c>
       <c r="D116" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="F116" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G116">
         <v>115</v>
@@ -7522,10 +7531,10 @@
         <v>834</v>
       </c>
       <c r="D117" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="F117" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G117">
         <v>116</v>
@@ -7548,10 +7557,10 @@
         <v>835</v>
       </c>
       <c r="D118" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="F118" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G118">
         <v>117</v>
@@ -7574,10 +7583,10 @@
         <v>836</v>
       </c>
       <c r="D119" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="F119" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G119">
         <v>118</v>
@@ -7600,10 +7609,10 @@
         <v>837</v>
       </c>
       <c r="D120" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="F120" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G120">
         <v>119</v>
@@ -7626,10 +7635,10 @@
         <v>838</v>
       </c>
       <c r="D121" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="F121" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G121">
         <v>120</v>
@@ -7652,10 +7661,10 @@
         <v>839</v>
       </c>
       <c r="D122" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="F122" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G122">
         <v>121</v>
@@ -7678,10 +7687,10 @@
         <v>840</v>
       </c>
       <c r="D123" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="F123" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G123">
         <v>122</v>
@@ -7704,10 +7713,10 @@
         <v>841</v>
       </c>
       <c r="D124" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="F124" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G124">
         <v>123</v>
@@ -7730,10 +7739,10 @@
         <v>842</v>
       </c>
       <c r="D125" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="F125" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G125">
         <v>124</v>
@@ -7756,10 +7765,10 @@
         <v>843</v>
       </c>
       <c r="D126" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="F126" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G126">
         <v>125</v>
@@ -7782,10 +7791,10 @@
         <v>844</v>
       </c>
       <c r="D127" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="F127" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G127">
         <v>126</v>
@@ -7808,10 +7817,10 @@
         <v>845</v>
       </c>
       <c r="D128" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="F128" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G128">
         <v>127</v>
@@ -7834,10 +7843,10 @@
         <v>846</v>
       </c>
       <c r="D129" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="F129" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G129">
         <v>128</v>
@@ -7860,10 +7869,10 @@
         <v>847</v>
       </c>
       <c r="D130" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="F130" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G130">
         <v>129</v>
@@ -7886,10 +7895,10 @@
         <v>848</v>
       </c>
       <c r="D131" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F131" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G131">
         <v>130</v>
@@ -7912,10 +7921,10 @@
         <v>849</v>
       </c>
       <c r="D132" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="F132" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G132">
         <v>131</v>
@@ -7938,10 +7947,10 @@
         <v>850</v>
       </c>
       <c r="D133" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="F133" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G133">
         <v>132</v>
@@ -7964,10 +7973,10 @@
         <v>851</v>
       </c>
       <c r="D134" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="F134" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G134">
         <v>133</v>
@@ -7990,10 +7999,10 @@
         <v>852</v>
       </c>
       <c r="D135" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="F135" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G135">
         <v>134</v>
@@ -8016,10 +8025,10 @@
         <v>853</v>
       </c>
       <c r="D136" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="F136" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G136">
         <v>135</v>
@@ -8042,10 +8051,10 @@
         <v>854</v>
       </c>
       <c r="D137" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="F137" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G137">
         <v>136</v>
@@ -8068,10 +8077,10 @@
         <v>855</v>
       </c>
       <c r="D138" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="F138" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G138">
         <v>137</v>
@@ -8094,10 +8103,10 @@
         <v>856</v>
       </c>
       <c r="D139" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="F139" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G139">
         <v>138</v>
@@ -8120,10 +8129,10 @@
         <v>857</v>
       </c>
       <c r="D140" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="F140" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G140">
         <v>139</v>
@@ -8146,10 +8155,10 @@
         <v>858</v>
       </c>
       <c r="D141" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="F141" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G141">
         <v>140</v>
@@ -8172,10 +8181,10 @@
         <v>859</v>
       </c>
       <c r="D142" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="F142" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G142">
         <v>141</v>
@@ -8198,10 +8207,10 @@
         <v>860</v>
       </c>
       <c r="D143" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="F143" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G143">
         <v>142</v>
@@ -8224,10 +8233,10 @@
         <v>861</v>
       </c>
       <c r="D144" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="F144" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G144">
         <v>143</v>
@@ -8250,10 +8259,10 @@
         <v>862</v>
       </c>
       <c r="D145" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="F145" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G145">
         <v>144</v>
@@ -8276,10 +8285,10 @@
         <v>863</v>
       </c>
       <c r="D146" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="F146" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G146">
         <v>145</v>
@@ -8302,10 +8311,10 @@
         <v>864</v>
       </c>
       <c r="D147" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="F147" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G147">
         <v>146</v>
@@ -8328,10 +8337,10 @@
         <v>865</v>
       </c>
       <c r="D148" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="F148" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G148">
         <v>147</v>
@@ -8354,10 +8363,10 @@
         <v>866</v>
       </c>
       <c r="D149" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="F149" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G149">
         <v>148</v>
@@ -8380,10 +8389,10 @@
         <v>867</v>
       </c>
       <c r="D150" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="F150" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G150">
         <v>149</v>
@@ -8406,10 +8415,10 @@
         <v>868</v>
       </c>
       <c r="D151" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="F151" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G151">
         <v>150</v>
@@ -8432,10 +8441,10 @@
         <v>869</v>
       </c>
       <c r="D152" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="F152" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G152">
         <v>151</v>
@@ -8458,10 +8467,10 @@
         <v>870</v>
       </c>
       <c r="D153" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="F153" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G153">
         <v>152</v>
@@ -8484,10 +8493,10 @@
         <v>871</v>
       </c>
       <c r="D154" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="F154" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G154">
         <v>153</v>
@@ -8510,10 +8519,10 @@
         <v>872</v>
       </c>
       <c r="D155" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="F155" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G155">
         <v>154</v>
@@ -8536,10 +8545,10 @@
         <v>873</v>
       </c>
       <c r="D156" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="F156" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G156">
         <v>155</v>
@@ -8562,10 +8571,10 @@
         <v>874</v>
       </c>
       <c r="D157" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="F157" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G157">
         <v>156</v>
@@ -8588,10 +8597,10 @@
         <v>875</v>
       </c>
       <c r="D158" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="F158" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G158">
         <v>157</v>
@@ -8614,10 +8623,10 @@
         <v>876</v>
       </c>
       <c r="D159" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="F159" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G159">
         <v>158</v>
@@ -8640,10 +8649,10 @@
         <v>877</v>
       </c>
       <c r="D160" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="F160" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G160">
         <v>159</v>
@@ -8666,10 +8675,10 @@
         <v>878</v>
       </c>
       <c r="D161" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="F161" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G161">
         <v>160</v>
@@ -8692,10 +8701,10 @@
         <v>879</v>
       </c>
       <c r="D162" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="F162" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G162">
         <v>161</v>
@@ -8718,10 +8727,10 @@
         <v>880</v>
       </c>
       <c r="D163" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="F163" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G163">
         <v>162</v>
@@ -8744,10 +8753,10 @@
         <v>881</v>
       </c>
       <c r="D164" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="F164" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G164">
         <v>163</v>
@@ -8770,10 +8779,10 @@
         <v>882</v>
       </c>
       <c r="D165" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="F165" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G165">
         <v>164</v>
@@ -8796,10 +8805,10 @@
         <v>883</v>
       </c>
       <c r="D166" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="F166" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G166">
         <v>165</v>
@@ -8822,10 +8831,10 @@
         <v>884</v>
       </c>
       <c r="D167" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="F167" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G167">
         <v>166</v>
@@ -8848,10 +8857,10 @@
         <v>885</v>
       </c>
       <c r="D168" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="F168" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G168">
         <v>167</v>
@@ -8874,10 +8883,10 @@
         <v>886</v>
       </c>
       <c r="D169" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="F169" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G169">
         <v>168</v>
@@ -8900,10 +8909,10 @@
         <v>887</v>
       </c>
       <c r="D170" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="F170" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G170">
         <v>169</v>
@@ -8926,10 +8935,10 @@
         <v>888</v>
       </c>
       <c r="D171" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="F171" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G171">
         <v>170</v>
@@ -8952,10 +8961,10 @@
         <v>889</v>
       </c>
       <c r="D172" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="F172" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G172">
         <v>171</v>
@@ -8978,10 +8987,10 @@
         <v>890</v>
       </c>
       <c r="D173" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="F173" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G173">
         <v>172</v>
@@ -9004,10 +9013,10 @@
         <v>891</v>
       </c>
       <c r="D174" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="F174" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G174">
         <v>173</v>
@@ -9030,10 +9039,10 @@
         <v>892</v>
       </c>
       <c r="D175" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="F175" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G175">
         <v>174</v>
@@ -9056,10 +9065,10 @@
         <v>893</v>
       </c>
       <c r="D176" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="F176" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G176">
         <v>175</v>
@@ -9082,10 +9091,10 @@
         <v>894</v>
       </c>
       <c r="D177" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F177" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G177">
         <v>176</v>
@@ -9108,10 +9117,10 @@
         <v>895</v>
       </c>
       <c r="D178" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="F178" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G178">
         <v>177</v>
@@ -9134,10 +9143,10 @@
         <v>896</v>
       </c>
       <c r="D179" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="F179" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G179">
         <v>178</v>
@@ -9160,10 +9169,10 @@
         <v>897</v>
       </c>
       <c r="D180" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="F180" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G180">
         <v>179</v>
@@ -9186,10 +9195,10 @@
         <v>898</v>
       </c>
       <c r="D181" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="F181" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G181">
         <v>180</v>
@@ -9212,10 +9221,10 @@
         <v>899</v>
       </c>
       <c r="D182" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="F182" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G182">
         <v>181</v>
@@ -9238,10 +9247,10 @@
         <v>900</v>
       </c>
       <c r="D183" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="F183" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G183">
         <v>182</v>
@@ -9264,10 +9273,10 @@
         <v>901</v>
       </c>
       <c r="D184" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="F184" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G184">
         <v>183</v>
@@ -9290,10 +9299,10 @@
         <v>902</v>
       </c>
       <c r="D185" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="F185" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G185">
         <v>184</v>
@@ -9316,10 +9325,10 @@
         <v>903</v>
       </c>
       <c r="D186" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="F186" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G186">
         <v>185</v>
@@ -9342,10 +9351,10 @@
         <v>904</v>
       </c>
       <c r="D187" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="F187" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G187">
         <v>186</v>
@@ -9368,10 +9377,10 @@
         <v>905</v>
       </c>
       <c r="D188" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="F188" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G188">
         <v>187</v>
@@ -9394,10 +9403,10 @@
         <v>906</v>
       </c>
       <c r="D189" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="F189" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G189">
         <v>188</v>
@@ -9420,10 +9429,10 @@
         <v>907</v>
       </c>
       <c r="D190" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="F190" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G190">
         <v>189</v>
@@ -9446,10 +9455,10 @@
         <v>908</v>
       </c>
       <c r="D191" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F191" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G191">
         <v>190</v>
@@ -9472,10 +9481,10 @@
         <v>909</v>
       </c>
       <c r="D192" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="F192" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G192">
         <v>191</v>
@@ -9498,10 +9507,10 @@
         <v>910</v>
       </c>
       <c r="D193" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="F193" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G193">
         <v>192</v>
@@ -9524,10 +9533,10 @@
         <v>911</v>
       </c>
       <c r="D194" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="F194" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G194">
         <v>193</v>
@@ -9550,10 +9559,10 @@
         <v>912</v>
       </c>
       <c r="D195" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="F195" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G195">
         <v>194</v>
@@ -9576,10 +9585,10 @@
         <v>913</v>
       </c>
       <c r="D196" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="F196" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G196">
         <v>195</v>
@@ -9602,10 +9611,10 @@
         <v>914</v>
       </c>
       <c r="D197" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="F197" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G197">
         <v>196</v>
@@ -9628,10 +9637,10 @@
         <v>915</v>
       </c>
       <c r="D198" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="F198" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G198">
         <v>197</v>
@@ -9654,10 +9663,10 @@
         <v>916</v>
       </c>
       <c r="D199" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="F199" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G199">
         <v>198</v>
@@ -9680,10 +9689,10 @@
         <v>917</v>
       </c>
       <c r="D200" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="F200" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G200">
         <v>199</v>
@@ -9706,10 +9715,10 @@
         <v>918</v>
       </c>
       <c r="D201" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="F201" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G201">
         <v>200</v>
@@ -9732,10 +9741,10 @@
         <v>919</v>
       </c>
       <c r="D202" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="F202" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G202">
         <v>201</v>
@@ -9758,10 +9767,10 @@
         <v>920</v>
       </c>
       <c r="D203" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="F203" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G203">
         <v>202</v>
@@ -9784,10 +9793,10 @@
         <v>921</v>
       </c>
       <c r="D204" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="F204" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G204">
         <v>203</v>
@@ -9810,10 +9819,10 @@
         <v>922</v>
       </c>
       <c r="D205" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="F205" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G205">
         <v>204</v>
@@ -9836,10 +9845,10 @@
         <v>923</v>
       </c>
       <c r="D206" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="F206" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G206">
         <v>205</v>
@@ -9862,10 +9871,10 @@
         <v>924</v>
       </c>
       <c r="D207" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="F207" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G207">
         <v>206</v>
@@ -9888,10 +9897,10 @@
         <v>925</v>
       </c>
       <c r="D208" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="F208" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G208">
         <v>207</v>
@@ -9914,10 +9923,10 @@
         <v>926</v>
       </c>
       <c r="D209" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="F209" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G209">
         <v>208</v>
@@ -9940,10 +9949,10 @@
         <v>927</v>
       </c>
       <c r="D210" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="F210" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G210">
         <v>209</v>
@@ -9966,10 +9975,10 @@
         <v>928</v>
       </c>
       <c r="D211" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="F211" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G211">
         <v>210</v>
@@ -9992,10 +10001,10 @@
         <v>929</v>
       </c>
       <c r="D212" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="F212" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G212">
         <v>211</v>
@@ -10018,10 +10027,10 @@
         <v>930</v>
       </c>
       <c r="D213" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="F213" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G213">
         <v>212</v>
@@ -10044,10 +10053,10 @@
         <v>931</v>
       </c>
       <c r="D214" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="F214" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G214">
         <v>213</v>
@@ -10070,10 +10079,10 @@
         <v>932</v>
       </c>
       <c r="D215" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="F215" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G215">
         <v>214</v>
@@ -10096,10 +10105,10 @@
         <v>933</v>
       </c>
       <c r="D216" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="F216" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G216">
         <v>215</v>
@@ -10122,10 +10131,10 @@
         <v>934</v>
       </c>
       <c r="D217" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="F217" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G217">
         <v>216</v>
@@ -10148,10 +10157,10 @@
         <v>935</v>
       </c>
       <c r="D218" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="F218" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G218">
         <v>217</v>
@@ -10174,10 +10183,10 @@
         <v>936</v>
       </c>
       <c r="D219" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="F219" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G219">
         <v>218</v>
@@ -10200,10 +10209,10 @@
         <v>937</v>
       </c>
       <c r="D220" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F220" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G220">
         <v>219</v>
@@ -10226,10 +10235,10 @@
         <v>938</v>
       </c>
       <c r="D221" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="F221" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G221">
         <v>220</v>
@@ -10252,10 +10261,10 @@
         <v>939</v>
       </c>
       <c r="D222" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="F222" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G222">
         <v>221</v>
@@ -10278,10 +10287,10 @@
         <v>940</v>
       </c>
       <c r="D223" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="F223" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G223">
         <v>222</v>
@@ -10304,10 +10313,10 @@
         <v>941</v>
       </c>
       <c r="D224" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="F224" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G224">
         <v>223</v>
@@ -10330,10 +10339,10 @@
         <v>942</v>
       </c>
       <c r="D225" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="F225" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G225">
         <v>224</v>
@@ -10356,10 +10365,10 @@
         <v>943</v>
       </c>
       <c r="D226" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="F226" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G226">
         <v>225</v>
@@ -10382,10 +10391,10 @@
         <v>944</v>
       </c>
       <c r="D227" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="F227" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G227">
         <v>226</v>
@@ -10408,10 +10417,10 @@
         <v>945</v>
       </c>
       <c r="D228" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="F228" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G228">
         <v>227</v>
@@ -10434,10 +10443,10 @@
         <v>946</v>
       </c>
       <c r="D229" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="F229" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G229">
         <v>228</v>
@@ -10460,10 +10469,10 @@
         <v>947</v>
       </c>
       <c r="D230" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="F230" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G230">
         <v>229</v>
@@ -10486,10 +10495,10 @@
         <v>948</v>
       </c>
       <c r="D231" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="F231" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G231">
         <v>230</v>
@@ -10512,10 +10521,10 @@
         <v>949</v>
       </c>
       <c r="D232" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="F232" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G232">
         <v>231</v>
@@ -10538,10 +10547,10 @@
         <v>950</v>
       </c>
       <c r="D233" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="F233" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G233">
         <v>232</v>
@@ -10564,10 +10573,10 @@
         <v>951</v>
       </c>
       <c r="D234" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="F234" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G234">
         <v>233</v>
@@ -10590,10 +10599,10 @@
         <v>952</v>
       </c>
       <c r="D235" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="F235" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G235">
         <v>234</v>
@@ -10616,10 +10625,10 @@
         <v>953</v>
       </c>
       <c r="D236" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="F236" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G236">
         <v>235</v>
@@ -10642,10 +10651,10 @@
         <v>954</v>
       </c>
       <c r="D237" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="F237" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G237">
         <v>236</v>
@@ -10668,10 +10677,10 @@
         <v>955</v>
       </c>
       <c r="D238" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="F238" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G238">
         <v>237</v>
@@ -10694,10 +10703,10 @@
         <v>956</v>
       </c>
       <c r="D239" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="F239" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G239">
         <v>238</v>
@@ -10720,10 +10729,10 @@
         <v>957</v>
       </c>
       <c r="D240" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="F240" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G240">
         <v>239</v>
@@ -10746,10 +10755,10 @@
         <v>958</v>
       </c>
       <c r="D241" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="F241" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G241">
         <v>240</v>
@@ -10772,10 +10781,10 @@
         <v>959</v>
       </c>
       <c r="D242" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="F242" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G242">
         <v>241</v>
@@ -10798,10 +10807,10 @@
         <v>960</v>
       </c>
       <c r="D243" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="F243" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G243">
         <v>242</v>
@@ -10824,10 +10833,10 @@
         <v>961</v>
       </c>
       <c r="D244" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="F244" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G244">
         <v>243</v>
@@ -10850,10 +10859,10 @@
         <v>962</v>
       </c>
       <c r="D245" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="F245" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G245">
         <v>244</v>
@@ -10876,10 +10885,10 @@
         <v>963</v>
       </c>
       <c r="D246" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="F246" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G246">
         <v>245</v>
@@ -10902,10 +10911,10 @@
         <v>964</v>
       </c>
       <c r="D247" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="F247" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G247">
         <v>246</v>
@@ -10928,10 +10937,10 @@
         <v>965</v>
       </c>
       <c r="D248" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="F248" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G248">
         <v>247</v>
@@ -10954,10 +10963,10 @@
         <v>966</v>
       </c>
       <c r="D249" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="F249" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G249">
         <v>248</v>
@@ -10980,10 +10989,10 @@
         <v>967</v>
       </c>
       <c r="D250" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="F250" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G250">
         <v>249</v>
@@ -11006,10 +11015,10 @@
         <v>968</v>
       </c>
       <c r="D251" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="F251" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G251">
         <v>250</v>
@@ -11032,10 +11041,10 @@
         <v>969</v>
       </c>
       <c r="D252" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="F252" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G252">
         <v>251</v>
@@ -11058,10 +11067,10 @@
         <v>970</v>
       </c>
       <c r="D253" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="F253" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G253">
         <v>252</v>
@@ -11084,10 +11093,10 @@
         <v>971</v>
       </c>
       <c r="D254" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="F254" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G254">
         <v>253</v>
@@ -11110,10 +11119,10 @@
         <v>972</v>
       </c>
       <c r="D255" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="F255" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G255">
         <v>254</v>
@@ -11136,10 +11145,10 @@
         <v>973</v>
       </c>
       <c r="D256" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F256" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G256">
         <v>255</v>
@@ -11162,10 +11171,10 @@
         <v>974</v>
       </c>
       <c r="D257" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F257" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G257">
         <v>256</v>
@@ -11188,10 +11197,10 @@
         <v>975</v>
       </c>
       <c r="D258" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="F258" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G258">
         <v>257</v>
@@ -11214,10 +11223,10 @@
         <v>976</v>
       </c>
       <c r="D259" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="F259" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G259">
         <v>258</v>
@@ -11240,10 +11249,10 @@
         <v>977</v>
       </c>
       <c r="D260" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="F260" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G260">
         <v>259</v>
@@ -11266,10 +11275,10 @@
         <v>978</v>
       </c>
       <c r="D261" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="F261" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G261">
         <v>260</v>
@@ -11292,10 +11301,10 @@
         <v>979</v>
       </c>
       <c r="D262" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="F262" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G262">
         <v>261</v>
@@ -11318,10 +11327,10 @@
         <v>980</v>
       </c>
       <c r="D263" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="F263" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G263">
         <v>262</v>
@@ -11344,10 +11353,10 @@
         <v>981</v>
       </c>
       <c r="D264" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="F264" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G264">
         <v>263</v>
@@ -11370,10 +11379,10 @@
         <v>982</v>
       </c>
       <c r="D265" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="F265" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G265">
         <v>264</v>
@@ -11396,10 +11405,10 @@
         <v>983</v>
       </c>
       <c r="D266" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="F266" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G266">
         <v>265</v>
@@ -11422,10 +11431,10 @@
         <v>984</v>
       </c>
       <c r="D267" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="F267" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G267">
         <v>266</v>
@@ -11448,10 +11457,10 @@
         <v>985</v>
       </c>
       <c r="D268" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="F268" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G268">
         <v>267</v>
@@ -11474,10 +11483,10 @@
         <v>986</v>
       </c>
       <c r="D269" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="F269" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G269">
         <v>268</v>
@@ -11500,10 +11509,10 @@
         <v>987</v>
       </c>
       <c r="D270" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="F270" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G270">
         <v>269</v>
@@ -11526,10 +11535,10 @@
         <v>988</v>
       </c>
       <c r="D271" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="F271" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G271">
         <v>270</v>
@@ -11552,10 +11561,10 @@
         <v>989</v>
       </c>
       <c r="D272" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="F272" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G272">
         <v>271</v>
@@ -11578,10 +11587,10 @@
         <v>990</v>
       </c>
       <c r="D273" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="F273" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G273">
         <v>272</v>
@@ -11604,10 +11613,10 @@
         <v>991</v>
       </c>
       <c r="D274" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="F274" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G274">
         <v>273</v>
@@ -11630,10 +11639,10 @@
         <v>992</v>
       </c>
       <c r="D275" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="F275" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G275">
         <v>274</v>
@@ -11656,10 +11665,10 @@
         <v>993</v>
       </c>
       <c r="D276" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="F276" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G276">
         <v>275</v>
@@ -11682,10 +11691,10 @@
         <v>994</v>
       </c>
       <c r="D277" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="F277" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G277">
         <v>276</v>
@@ -11708,10 +11717,10 @@
         <v>995</v>
       </c>
       <c r="D278" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="F278" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G278">
         <v>277</v>
@@ -11734,10 +11743,10 @@
         <v>996</v>
       </c>
       <c r="D279" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="F279" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G279">
         <v>278</v>
@@ -11760,10 +11769,10 @@
         <v>997</v>
       </c>
       <c r="D280" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="F280" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G280">
         <v>279</v>
@@ -11786,10 +11795,10 @@
         <v>998</v>
       </c>
       <c r="D281" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="F281" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G281">
         <v>280</v>
@@ -11812,10 +11821,10 @@
         <v>999</v>
       </c>
       <c r="D282" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="F282" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G282">
         <v>281</v>
@@ -11838,10 +11847,10 @@
         <v>1000</v>
       </c>
       <c r="D283" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="F283" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G283">
         <v>282</v>
@@ -11864,10 +11873,10 @@
         <v>1001</v>
       </c>
       <c r="D284" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="F284" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G284">
         <v>283</v>
@@ -11890,10 +11899,10 @@
         <v>1002</v>
       </c>
       <c r="D285" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="F285" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G285">
         <v>284</v>
@@ -11916,10 +11925,10 @@
         <v>1003</v>
       </c>
       <c r="D286" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="F286" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G286">
         <v>285</v>
@@ -11942,10 +11951,10 @@
         <v>1004</v>
       </c>
       <c r="D287" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="F287" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G287">
         <v>286</v>
@@ -11968,10 +11977,10 @@
         <v>1005</v>
       </c>
       <c r="D288" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="F288" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G288">
         <v>287</v>
@@ -11994,10 +12003,10 @@
         <v>1006</v>
       </c>
       <c r="D289" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="F289" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G289">
         <v>288</v>
@@ -12020,10 +12029,10 @@
         <v>1007</v>
       </c>
       <c r="D290" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="F290" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G290">
         <v>289</v>
@@ -12046,10 +12055,10 @@
         <v>1008</v>
       </c>
       <c r="D291" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="F291" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G291">
         <v>290</v>
@@ -12072,10 +12081,10 @@
         <v>1009</v>
       </c>
       <c r="D292" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="F292" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G292">
         <v>291</v>
@@ -12098,10 +12107,10 @@
         <v>1010</v>
       </c>
       <c r="D293" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="F293" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G293">
         <v>292</v>
@@ -12124,10 +12133,10 @@
         <v>1011</v>
       </c>
       <c r="D294" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="F294" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G294">
         <v>293</v>
@@ -12150,10 +12159,10 @@
         <v>1012</v>
       </c>
       <c r="D295" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="F295" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G295">
         <v>294</v>
@@ -12176,10 +12185,10 @@
         <v>1013</v>
       </c>
       <c r="D296" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="F296" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G296">
         <v>295</v>
@@ -12202,10 +12211,10 @@
         <v>1014</v>
       </c>
       <c r="D297" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="F297" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G297">
         <v>296</v>
@@ -12228,10 +12237,10 @@
         <v>1015</v>
       </c>
       <c r="D298" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="F298" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G298">
         <v>297</v>
@@ -12254,10 +12263,10 @@
         <v>1016</v>
       </c>
       <c r="D299" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="F299" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G299">
         <v>298</v>
@@ -12280,10 +12289,10 @@
         <v>1017</v>
       </c>
       <c r="D300" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="F300" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G300">
         <v>299</v>
@@ -12306,10 +12315,10 @@
         <v>1018</v>
       </c>
       <c r="D301" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="F301" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G301">
         <v>300</v>
@@ -12332,10 +12341,10 @@
         <v>1019</v>
       </c>
       <c r="D302" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="F302" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G302">
         <v>301</v>
@@ -12358,10 +12367,10 @@
         <v>1020</v>
       </c>
       <c r="D303" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="F303" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G303">
         <v>302</v>
@@ -12384,10 +12393,10 @@
         <v>1021</v>
       </c>
       <c r="D304" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="F304" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G304">
         <v>303</v>
@@ -12410,10 +12419,10 @@
         <v>1022</v>
       </c>
       <c r="D305" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="F305" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G305">
         <v>304</v>
@@ -12436,10 +12445,10 @@
         <v>1023</v>
       </c>
       <c r="D306" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="F306" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G306">
         <v>305</v>
@@ -12462,10 +12471,10 @@
         <v>1024</v>
       </c>
       <c r="D307" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="F307" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G307">
         <v>306</v>
@@ -12488,10 +12497,10 @@
         <v>1025</v>
       </c>
       <c r="D308" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="F308" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G308">
         <v>307</v>
@@ -12514,10 +12523,10 @@
         <v>1026</v>
       </c>
       <c r="D309" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="F309" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G309">
         <v>308</v>
@@ -12540,10 +12549,10 @@
         <v>1027</v>
       </c>
       <c r="D310" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="F310" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G310">
         <v>309</v>
@@ -12566,10 +12575,10 @@
         <v>1028</v>
       </c>
       <c r="D311" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="F311" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G311">
         <v>310</v>
@@ -12592,10 +12601,10 @@
         <v>1029</v>
       </c>
       <c r="D312" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="F312" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G312">
         <v>311</v>
@@ -12618,10 +12627,10 @@
         <v>1030</v>
       </c>
       <c r="D313" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="F313" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G313">
         <v>312</v>
@@ -12644,10 +12653,10 @@
         <v>1031</v>
       </c>
       <c r="D314" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="F314" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G314">
         <v>313</v>
@@ -12670,10 +12679,10 @@
         <v>1032</v>
       </c>
       <c r="D315" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="F315" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G315">
         <v>314</v>
@@ -12696,10 +12705,10 @@
         <v>1033</v>
       </c>
       <c r="D316" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="F316" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G316">
         <v>315</v>
@@ -12722,10 +12731,10 @@
         <v>1034</v>
       </c>
       <c r="D317" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="F317" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G317">
         <v>316</v>
@@ -12748,10 +12757,10 @@
         <v>1035</v>
       </c>
       <c r="D318" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="F318" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G318">
         <v>317</v>
@@ -12774,10 +12783,10 @@
         <v>1036</v>
       </c>
       <c r="D319" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="F319" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G319">
         <v>318</v>
@@ -12800,10 +12809,10 @@
         <v>1037</v>
       </c>
       <c r="D320" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="F320" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G320">
         <v>319</v>
@@ -12826,10 +12835,10 @@
         <v>1038</v>
       </c>
       <c r="D321" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="F321" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G321">
         <v>320</v>
@@ -12852,10 +12861,10 @@
         <v>1039</v>
       </c>
       <c r="D322" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="F322" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G322">
         <v>321</v>
@@ -12878,10 +12887,10 @@
         <v>1040</v>
       </c>
       <c r="D323" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="F323" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G323">
         <v>322</v>
@@ -12904,10 +12913,10 @@
         <v>1041</v>
       </c>
       <c r="D324" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="F324" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G324">
         <v>323</v>
@@ -12930,10 +12939,10 @@
         <v>1042</v>
       </c>
       <c r="D325" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="F325" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G325">
         <v>324</v>
@@ -12956,10 +12965,10 @@
         <v>1043</v>
       </c>
       <c r="D326" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="F326" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G326">
         <v>325</v>
@@ -12982,10 +12991,10 @@
         <v>1044</v>
       </c>
       <c r="D327" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="F327" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G327">
         <v>326</v>
@@ -13008,10 +13017,10 @@
         <v>1045</v>
       </c>
       <c r="D328" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="F328" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G328">
         <v>327</v>
@@ -13034,10 +13043,10 @@
         <v>1046</v>
       </c>
       <c r="D329" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="F329" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G329">
         <v>328</v>
@@ -13060,10 +13069,10 @@
         <v>1047</v>
       </c>
       <c r="D330" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="F330" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G330">
         <v>329</v>
@@ -13086,10 +13095,10 @@
         <v>1048</v>
       </c>
       <c r="D331" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="F331" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G331">
         <v>330</v>
@@ -13112,10 +13121,10 @@
         <v>1049</v>
       </c>
       <c r="D332" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="F332" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G332">
         <v>331</v>
@@ -13138,10 +13147,10 @@
         <v>1050</v>
       </c>
       <c r="D333" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="F333" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G333">
         <v>332</v>
@@ -13164,10 +13173,10 @@
         <v>1051</v>
       </c>
       <c r="D334" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="F334" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G334">
         <v>333</v>
@@ -13190,10 +13199,10 @@
         <v>1052</v>
       </c>
       <c r="D335" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="F335" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G335">
         <v>334</v>
@@ -13216,10 +13225,10 @@
         <v>1053</v>
       </c>
       <c r="D336" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="F336" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G336">
         <v>335</v>
@@ -13242,10 +13251,10 @@
         <v>1054</v>
       </c>
       <c r="D337" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="F337" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G337">
         <v>336</v>
@@ -13268,10 +13277,10 @@
         <v>1055</v>
       </c>
       <c r="D338" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F338" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G338">
         <v>337</v>
@@ -13294,10 +13303,10 @@
         <v>1056</v>
       </c>
       <c r="D339" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="F339" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G339">
         <v>338</v>
@@ -13320,10 +13329,10 @@
         <v>1057</v>
       </c>
       <c r="D340" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="F340" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G340">
         <v>339</v>
@@ -13346,10 +13355,10 @@
         <v>1058</v>
       </c>
       <c r="D341" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="F341" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G341">
         <v>340</v>
@@ -13372,10 +13381,10 @@
         <v>1059</v>
       </c>
       <c r="D342" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="F342" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G342">
         <v>341</v>
@@ -13398,10 +13407,10 @@
         <v>1060</v>
       </c>
       <c r="D343" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="F343" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G343">
         <v>342</v>
@@ -13424,10 +13433,10 @@
         <v>1061</v>
       </c>
       <c r="D344" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="F344" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G344">
         <v>343</v>
@@ -13450,10 +13459,10 @@
         <v>1062</v>
       </c>
       <c r="D345" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="F345" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G345">
         <v>344</v>
@@ -13476,10 +13485,10 @@
         <v>1063</v>
       </c>
       <c r="D346" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="F346" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G346">
         <v>345</v>
@@ -13502,10 +13511,10 @@
         <v>1064</v>
       </c>
       <c r="D347" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="F347" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G347">
         <v>346</v>
@@ -13528,10 +13537,10 @@
         <v>1065</v>
       </c>
       <c r="D348" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="F348" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G348">
         <v>347</v>
@@ -13554,10 +13563,10 @@
         <v>1066</v>
       </c>
       <c r="D349" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="F349" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G349">
         <v>348</v>
@@ -13580,10 +13589,10 @@
         <v>1067</v>
       </c>
       <c r="D350" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="F350" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G350">
         <v>349</v>
@@ -13606,10 +13615,10 @@
         <v>1068</v>
       </c>
       <c r="D351" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="F351" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G351">
         <v>350</v>
@@ -13632,10 +13641,10 @@
         <v>1069</v>
       </c>
       <c r="D352" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="F352" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G352">
         <v>351</v>
@@ -13658,10 +13667,10 @@
         <v>1070</v>
       </c>
       <c r="D353" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="F353" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G353">
         <v>352</v>
@@ -13684,10 +13693,10 @@
         <v>1071</v>
       </c>
       <c r="D354" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="F354" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G354">
         <v>353</v>
@@ -13710,10 +13719,10 @@
         <v>1072</v>
       </c>
       <c r="D355" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="F355" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G355">
         <v>354</v>
@@ -13736,10 +13745,10 @@
         <v>1073</v>
       </c>
       <c r="D356" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="F356" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G356">
         <v>355</v>
@@ -13762,10 +13771,10 @@
         <v>1074</v>
       </c>
       <c r="D357" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="F357" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G357">
         <v>356</v>
@@ -13788,10 +13797,10 @@
         <v>1075</v>
       </c>
       <c r="D358" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="F358" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G358">
         <v>357</v>
@@ -13814,10 +13823,10 @@
         <v>1076</v>
       </c>
       <c r="D359" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="F359" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G359">
         <v>358</v>
@@ -13840,10 +13849,10 @@
         <v>1077</v>
       </c>
       <c r="D360" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="F360" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G360">
         <v>359</v>
@@ -13866,10 +13875,10 @@
         <v>1078</v>
       </c>
       <c r="D361" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="F361" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G361">
         <v>360</v>
@@ -13892,10 +13901,10 @@
         <v>1079</v>
       </c>
       <c r="D362" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="F362" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G362">
         <v>361</v>
@@ -13918,10 +13927,10 @@
         <v>1080</v>
       </c>
       <c r="D363" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="F363" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G363">
         <v>362</v>
@@ -13944,10 +13953,10 @@
         <v>1081</v>
       </c>
       <c r="D364" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="F364" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G364">
         <v>363</v>
@@ -13970,10 +13979,10 @@
         <v>1082</v>
       </c>
       <c r="D365" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="F365" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G365">
         <v>364</v>
@@ -13996,10 +14005,10 @@
         <v>1083</v>
       </c>
       <c r="D366" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="F366" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G366">
         <v>365</v>
@@ -14022,10 +14031,10 @@
         <v>1084</v>
       </c>
       <c r="D367" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="F367" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G367">
         <v>366</v>
@@ -14048,10 +14057,10 @@
         <v>1085</v>
       </c>
       <c r="D368" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="F368" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G368">
         <v>367</v>
@@ -14074,10 +14083,10 @@
         <v>1086</v>
       </c>
       <c r="D369" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="F369" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G369">
         <v>368</v>
@@ -14100,10 +14109,10 @@
         <v>1087</v>
       </c>
       <c r="D370" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="F370" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G370">
         <v>369</v>
@@ -14126,10 +14135,10 @@
         <v>1088</v>
       </c>
       <c r="D371" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="F371" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G371">
         <v>370</v>
@@ -14152,10 +14161,10 @@
         <v>1089</v>
       </c>
       <c r="D372" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="F372" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G372">
         <v>371</v>
@@ -14178,10 +14187,10 @@
         <v>1090</v>
       </c>
       <c r="D373" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="F373" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G373">
         <v>372</v>
@@ -14204,10 +14213,10 @@
         <v>1091</v>
       </c>
       <c r="D374" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="F374" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G374">
         <v>373</v>
@@ -14230,10 +14239,10 @@
         <v>1092</v>
       </c>
       <c r="D375" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="F375" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G375">
         <v>374</v>
@@ -14256,10 +14265,10 @@
         <v>1093</v>
       </c>
       <c r="D376" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="F376" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G376">
         <v>375</v>
@@ -14282,10 +14291,10 @@
         <v>1094</v>
       </c>
       <c r="D377" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="F377" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G377">
         <v>376</v>
@@ -14308,10 +14317,10 @@
         <v>1095</v>
       </c>
       <c r="D378" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="F378" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G378">
         <v>377</v>
@@ -14334,10 +14343,10 @@
         <v>1096</v>
       </c>
       <c r="D379" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="F379" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G379">
         <v>378</v>
@@ -14360,10 +14369,10 @@
         <v>1097</v>
       </c>
       <c r="D380" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="F380" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G380">
         <v>379</v>
@@ -14386,10 +14395,10 @@
         <v>1098</v>
       </c>
       <c r="D381" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="F381" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G381">
         <v>380</v>
@@ -14412,10 +14421,10 @@
         <v>1099</v>
       </c>
       <c r="D382" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="F382" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G382">
         <v>381</v>
@@ -14438,10 +14447,10 @@
         <v>1100</v>
       </c>
       <c r="D383" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="F383" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G383">
         <v>382</v>
@@ -14464,10 +14473,10 @@
         <v>1101</v>
       </c>
       <c r="D384" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="F384" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G384">
         <v>383</v>
@@ -14490,10 +14499,10 @@
         <v>1102</v>
       </c>
       <c r="D385" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="F385" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G385">
         <v>384</v>
@@ -14516,10 +14525,10 @@
         <v>1103</v>
       </c>
       <c r="D386" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F386" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G386">
         <v>385</v>
@@ -14542,10 +14551,10 @@
         <v>1104</v>
       </c>
       <c r="D387" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="F387" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G387">
         <v>386</v>
@@ -14568,10 +14577,10 @@
         <v>1105</v>
       </c>
       <c r="D388" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="F388" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G388">
         <v>387</v>
@@ -14594,10 +14603,10 @@
         <v>1106</v>
       </c>
       <c r="D389" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="F389" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G389">
         <v>388</v>
@@ -14620,10 +14629,10 @@
         <v>1107</v>
       </c>
       <c r="D390" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="F390" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G390">
         <v>389</v>
@@ -14646,10 +14655,10 @@
         <v>1108</v>
       </c>
       <c r="D391" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="F391" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G391">
         <v>390</v>
@@ -14672,10 +14681,10 @@
         <v>1109</v>
       </c>
       <c r="D392" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="F392" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G392">
         <v>391</v>
@@ -14698,10 +14707,10 @@
         <v>1110</v>
       </c>
       <c r="D393" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="F393" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G393">
         <v>392</v>
@@ -14724,10 +14733,10 @@
         <v>1111</v>
       </c>
       <c r="D394" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="F394" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G394">
         <v>393</v>
@@ -14750,10 +14759,10 @@
         <v>1112</v>
       </c>
       <c r="D395" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="F395" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G395">
         <v>394</v>
@@ -14776,10 +14785,10 @@
         <v>1113</v>
       </c>
       <c r="D396" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="F396" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G396">
         <v>395</v>
@@ -14802,10 +14811,10 @@
         <v>1114</v>
       </c>
       <c r="D397" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="F397" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G397">
         <v>396</v>
@@ -14828,10 +14837,10 @@
         <v>1115</v>
       </c>
       <c r="D398" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="F398" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G398">
         <v>397</v>
@@ -14854,10 +14863,10 @@
         <v>1116</v>
       </c>
       <c r="D399" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="F399" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G399">
         <v>398</v>
@@ -14880,10 +14889,10 @@
         <v>1117</v>
       </c>
       <c r="D400" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="F400" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G400">
         <v>399</v>
@@ -14906,10 +14915,10 @@
         <v>1118</v>
       </c>
       <c r="D401" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F401" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G401">
         <v>400</v>
@@ -14932,10 +14941,10 @@
         <v>1119</v>
       </c>
       <c r="D402" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="F402" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G402">
         <v>401</v>
@@ -14958,10 +14967,10 @@
         <v>1120</v>
       </c>
       <c r="D403" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="F403" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G403">
         <v>402</v>
@@ -14984,10 +14993,10 @@
         <v>1121</v>
       </c>
       <c r="D404" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="F404" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G404">
         <v>403</v>
@@ -15010,10 +15019,10 @@
         <v>1122</v>
       </c>
       <c r="D405" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="F405" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G405">
         <v>404</v>
@@ -15036,10 +15045,10 @@
         <v>1123</v>
       </c>
       <c r="D406" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="F406" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G406">
         <v>405</v>
@@ -15062,10 +15071,10 @@
         <v>1124</v>
       </c>
       <c r="D407" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="F407" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G407">
         <v>406</v>
@@ -15088,10 +15097,10 @@
         <v>1125</v>
       </c>
       <c r="D408" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="F408" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G408">
         <v>407</v>
@@ -15114,10 +15123,10 @@
         <v>1126</v>
       </c>
       <c r="D409" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="F409" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G409">
         <v>408</v>
@@ -15140,10 +15149,10 @@
         <v>1127</v>
       </c>
       <c r="D410" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="F410" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G410">
         <v>409</v>
@@ -15166,10 +15175,10 @@
         <v>1128</v>
       </c>
       <c r="D411" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="F411" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G411">
         <v>410</v>
@@ -15192,10 +15201,10 @@
         <v>1129</v>
       </c>
       <c r="D412" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="F412" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G412">
         <v>411</v>
@@ -15218,10 +15227,10 @@
         <v>1130</v>
       </c>
       <c r="D413" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="F413" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G413">
         <v>412</v>
@@ -15244,10 +15253,10 @@
         <v>1131</v>
       </c>
       <c r="D414" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="F414" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G414">
         <v>413</v>
@@ -15270,10 +15279,10 @@
         <v>1132</v>
       </c>
       <c r="D415" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="F415" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G415">
         <v>414</v>
@@ -15296,10 +15305,10 @@
         <v>1133</v>
       </c>
       <c r="D416" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="F416" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G416">
         <v>415</v>
@@ -15322,10 +15331,10 @@
         <v>1134</v>
       </c>
       <c r="D417" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="F417" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G417">
         <v>416</v>
@@ -15348,10 +15357,10 @@
         <v>1135</v>
       </c>
       <c r="D418" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="F418" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G418">
         <v>417</v>
@@ -15374,10 +15383,10 @@
         <v>1136</v>
       </c>
       <c r="D419" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="F419" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G419">
         <v>418</v>
@@ -15400,10 +15409,10 @@
         <v>1137</v>
       </c>
       <c r="D420" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="F420" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G420">
         <v>419</v>
@@ -15426,10 +15435,10 @@
         <v>1138</v>
       </c>
       <c r="D421" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="F421" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G421">
         <v>420</v>
@@ -15452,10 +15461,10 @@
         <v>1139</v>
       </c>
       <c r="D422" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="F422" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G422">
         <v>421</v>
@@ -15478,10 +15487,10 @@
         <v>1140</v>
       </c>
       <c r="D423" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="F423" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G423">
         <v>422</v>
@@ -15504,10 +15513,10 @@
         <v>1141</v>
       </c>
       <c r="D424" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F424" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G424">
         <v>423</v>
@@ -15530,10 +15539,10 @@
         <v>1142</v>
       </c>
       <c r="D425" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="F425" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G425">
         <v>424</v>
@@ -15556,10 +15565,10 @@
         <v>1143</v>
       </c>
       <c r="D426" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="F426" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G426">
         <v>425</v>
@@ -15582,10 +15591,10 @@
         <v>1144</v>
       </c>
       <c r="D427" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="F427" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G427">
         <v>426</v>
@@ -15608,10 +15617,10 @@
         <v>1145</v>
       </c>
       <c r="D428" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="F428" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G428">
         <v>427</v>
@@ -15634,10 +15643,10 @@
         <v>1146</v>
       </c>
       <c r="D429" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="F429" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G429">
         <v>428</v>
@@ -15660,10 +15669,10 @@
         <v>1147</v>
       </c>
       <c r="D430" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="F430" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G430">
         <v>429</v>
@@ -15686,10 +15695,10 @@
         <v>1148</v>
       </c>
       <c r="D431" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="F431" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G431">
         <v>430</v>
@@ -15712,10 +15721,10 @@
         <v>1149</v>
       </c>
       <c r="D432" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="F432" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G432">
         <v>431</v>
@@ -15738,10 +15747,10 @@
         <v>1150</v>
       </c>
       <c r="D433" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="F433" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G433">
         <v>432</v>
@@ -15764,10 +15773,10 @@
         <v>1151</v>
       </c>
       <c r="D434" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="F434" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G434">
         <v>433</v>
@@ -15790,10 +15799,10 @@
         <v>1152</v>
       </c>
       <c r="D435" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="F435" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G435">
         <v>434</v>
@@ -15816,10 +15825,10 @@
         <v>1153</v>
       </c>
       <c r="D436" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="F436" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G436">
         <v>435</v>
@@ -15842,10 +15851,10 @@
         <v>1154</v>
       </c>
       <c r="D437" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="F437" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G437">
         <v>436</v>
@@ -15868,10 +15877,10 @@
         <v>1155</v>
       </c>
       <c r="D438" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="F438" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G438">
         <v>437</v>
@@ -15894,10 +15903,10 @@
         <v>1156</v>
       </c>
       <c r="D439" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="F439" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G439">
         <v>438</v>
@@ -15920,10 +15929,10 @@
         <v>1157</v>
       </c>
       <c r="D440" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="F440" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G440">
         <v>439</v>
@@ -15946,10 +15955,10 @@
         <v>1158</v>
       </c>
       <c r="D441" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="F441" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G441">
         <v>440</v>
@@ -15972,10 +15981,10 @@
         <v>1159</v>
       </c>
       <c r="D442" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="F442" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G442">
         <v>441</v>
@@ -15998,10 +16007,10 @@
         <v>1160</v>
       </c>
       <c r="D443" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="F443" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G443">
         <v>442</v>
@@ -16024,10 +16033,10 @@
         <v>1161</v>
       </c>
       <c r="D444" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="F444" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G444">
         <v>443</v>
@@ -16050,10 +16059,10 @@
         <v>1162</v>
       </c>
       <c r="D445" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="F445" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G445">
         <v>444</v>
@@ -16076,10 +16085,10 @@
         <v>1163</v>
       </c>
       <c r="D446" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="F446" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G446">
         <v>445</v>
@@ -16102,10 +16111,10 @@
         <v>1164</v>
       </c>
       <c r="D447" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="F447" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G447">
         <v>446</v>
@@ -16128,10 +16137,10 @@
         <v>1165</v>
       </c>
       <c r="D448" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="F448" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G448">
         <v>447</v>
@@ -16154,10 +16163,10 @@
         <v>1166</v>
       </c>
       <c r="D449" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="F449" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G449">
         <v>448</v>
@@ -16180,10 +16189,10 @@
         <v>1167</v>
       </c>
       <c r="D450" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="F450" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G450">
         <v>449</v>
@@ -16206,10 +16215,10 @@
         <v>1168</v>
       </c>
       <c r="D451" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="F451" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G451">
         <v>450</v>
@@ -16232,10 +16241,10 @@
         <v>1169</v>
       </c>
       <c r="D452" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="F452" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G452">
         <v>451</v>
@@ -16258,10 +16267,10 @@
         <v>1170</v>
       </c>
       <c r="D453" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="F453" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G453">
         <v>452</v>
@@ -16284,10 +16293,10 @@
         <v>1171</v>
       </c>
       <c r="D454" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="F454" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G454">
         <v>453</v>
@@ -16310,10 +16319,10 @@
         <v>1172</v>
       </c>
       <c r="D455" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="F455" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G455">
         <v>454</v>
@@ -16336,10 +16345,10 @@
         <v>1173</v>
       </c>
       <c r="D456" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="F456" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G456">
         <v>455</v>
